--- a/data/trans_camb/P57_AF_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 10,86</t>
+          <t>-1,52; 11,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,89; 24,58</t>
+          <t>12,23; 25,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -5,63</t>
+          <t>-23,91; -5,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 8,08</t>
+          <t>-5,98; 7,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 19,12</t>
+          <t>6,48; 19,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,35; -4,34</t>
+          <t>-20,88; -3,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 7,78</t>
+          <t>-1,78; 7,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 20,43</t>
+          <t>11,46; 20,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,44; -7,52</t>
+          <t>-20,35; -7,06</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 23,19</t>
+          <t>-2,77; 24,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,69; 51,13</t>
+          <t>23,0; 53,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,95; -11,68</t>
+          <t>-46,35; -11,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 15,16</t>
+          <t>-10,14; 14,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 37,38</t>
+          <t>11,45; 36,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,67; -8,2</t>
+          <t>-36,35; -6,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 15,1</t>
+          <t>-3,16; 14,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 40,28</t>
+          <t>20,48; 40,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,37; -14,36</t>
+          <t>-37,19; -13,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 4,55</t>
+          <t>-6,07; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,75</t>
+          <t>11,41; 21,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 2,06</t>
+          <t>-12,48; 1,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,14</t>
+          <t>2,84; 14,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 21,56</t>
+          <t>11,14; 21,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,31; -7,46</t>
+          <t>-33,75; -7,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,46</t>
+          <t>-0,46; 7,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 20,56</t>
+          <t>12,97; 20,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,05; -5,42</t>
+          <t>-23,4; -5,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 8,14</t>
+          <t>-9,91; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,54; 39,4</t>
+          <t>18,7; 38,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 3,64</t>
+          <t>-21,19; 2,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 26,0</t>
+          <t>4,69; 26,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 39,86</t>
+          <t>18,41; 39,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,26; -13,23</t>
+          <t>-57,37; -14,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 13,36</t>
+          <t>-0,74; 12,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,0; 36,81</t>
+          <t>21,61; 35,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,54; -9,66</t>
+          <t>-39,58; -9,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 9,98</t>
+          <t>-0,91; 9,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 17,29</t>
+          <t>7,32; 18,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 1,38</t>
+          <t>-10,44; 1,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 10,95</t>
+          <t>0,34; 10,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 18,01</t>
+          <t>7,59; 18,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 0,36</t>
+          <t>-10,22; 0,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 9,16</t>
+          <t>1,1; 8,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 16,8</t>
+          <t>8,81; 16,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -0,94</t>
+          <t>-8,59; -0,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 17,24</t>
+          <t>-1,44; 16,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,78; 29,8</t>
+          <t>11,41; 31,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 2,42</t>
+          <t>-16,47; 2,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 20,18</t>
+          <t>0,73; 19,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 31,58</t>
+          <t>12,52; 32,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 0,77</t>
+          <t>-16,69; 0,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,79</t>
+          <t>1,77; 14,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 29,17</t>
+          <t>14,08; 27,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,17; -1,64</t>
+          <t>-13,72; -1,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 7,65</t>
+          <t>-4,73; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 19,57</t>
+          <t>8,21; 19,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-46,12; -3,8</t>
+          <t>-44,94; -3,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 16,55</t>
+          <t>5,13; 16,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 21,23</t>
+          <t>10,11; 21,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 0,19</t>
+          <t>-14,82; -0,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 10,28</t>
+          <t>2,49; 10,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 18,63</t>
+          <t>10,73; 18,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,72; -4,52</t>
+          <t>-33,71; -3,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 13,14</t>
+          <t>-7,31; 11,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,59; 33,55</t>
+          <t>12,39; 32,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,79; -6,16</t>
+          <t>-69,93; -5,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,9; 27,85</t>
+          <t>7,92; 28,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,41; 36,54</t>
+          <t>15,54; 36,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 0,3</t>
+          <t>-23,1; -0,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 17,32</t>
+          <t>3,93; 17,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,57; 31,39</t>
+          <t>16,68; 30,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -7,28</t>
+          <t>-52,07; -6,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 2,29</t>
+          <t>-11,43; 2,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,78</t>
+          <t>3,09; 16,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 3,73</t>
+          <t>-9,11; 3,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 8,51</t>
+          <t>-4,09; 9,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,72; 17,76</t>
+          <t>5,72; 18,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 2,72</t>
+          <t>-8,57; 2,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,83</t>
+          <t>-5,87; 3,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 15,05</t>
+          <t>6,11; 15,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 1,43</t>
+          <t>-6,59; 1,69</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 3,75</t>
+          <t>-16,72; 4,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,02; 26,18</t>
+          <t>4,67; 26,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 6,2</t>
+          <t>-13,57; 5,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 13,48</t>
+          <t>-5,92; 14,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,32; 28,66</t>
+          <t>8,27; 29,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 4,16</t>
+          <t>-12,32; 4,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 6,09</t>
+          <t>-8,84; 6,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,37; 23,92</t>
+          <t>9,19; 24,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 2,28</t>
+          <t>-9,8; 2,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 7,05</t>
+          <t>-8,1; 7,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 11,54</t>
+          <t>-3,09; 12,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 0,69</t>
+          <t>-11,72; 2,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 12,68</t>
+          <t>-0,73; 13,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,13; 22,65</t>
+          <t>9,68; 22,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 29,49</t>
+          <t>-5,89; 27,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 7,66</t>
+          <t>-2,66; 7,86</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,06</t>
+          <t>5,36; 15,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 20,51</t>
+          <t>-5,96; 18,39</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 10,98</t>
+          <t>-11,36; 11,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 18,37</t>
+          <t>-4,21; 19,57</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 1,11</t>
+          <t>-16,51; 2,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 20,78</t>
+          <t>-1,16; 21,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,88; 37,03</t>
+          <t>14,38; 36,91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 49,85</t>
+          <t>-8,86; 46,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 11,99</t>
+          <t>-3,73; 12,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8,34; 23,8</t>
+          <t>8,02; 24,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 33,62</t>
+          <t>-8,84; 29,38</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 7,2</t>
+          <t>-9,97; 7,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 13,99</t>
+          <t>-1,52; 13,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 2,2</t>
+          <t>-13,16; 2,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 5,51</t>
+          <t>-9,41; 5,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,2; 20,79</t>
+          <t>7,38; 20,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 7,01</t>
+          <t>-4,92; 7,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 3,59</t>
+          <t>-7,75; 3,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,87; 15,99</t>
+          <t>5,65; 15,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,4</t>
+          <t>-6,65; 3,46</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 10,6</t>
+          <t>-13,03; 11,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 21,28</t>
+          <t>-1,91; 19,54</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 3,16</t>
+          <t>-17,12; 3,8</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 8,24</t>
+          <t>-12,7; 7,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,75; 31,83</t>
+          <t>9,91; 31,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 10,88</t>
+          <t>-6,55; 11,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 5,33</t>
+          <t>-10,54; 5,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7,98; 23,96</t>
+          <t>7,68; 23,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 4,98</t>
+          <t>-8,87; 5,12</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,62</t>
+          <t>-1,37; 3,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,82; 15,61</t>
+          <t>10,97; 15,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,79; -3,97</t>
+          <t>-20,43; -3,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,91</t>
+          <t>3,11; 7,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,11</t>
+          <t>12,67; 17,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,29</t>
+          <t>-7,13; 4,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,12</t>
+          <t>1,76; 5,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>12,5; 15,69</t>
+          <t>12,47; 15,73</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -1,96</t>
+          <t>-12,31; -1,77</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 6,13</t>
+          <t>-2,23; 6,36</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,34</t>
+          <t>17,65; 26,52</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -6,52</t>
+          <t>-32,62; -6,3</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,22</t>
+          <t>4,96; 13,03</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,23; 28,42</t>
+          <t>20,3; 28,95</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 7,1</t>
+          <t>-11,44; 8,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,48</t>
+          <t>2,82; 8,61</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>20,15; 26,15</t>
+          <t>20,29; 26,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -3,2</t>
+          <t>-19,9; -2,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AF_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_AF_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-15,03</t>
+          <t>-12,58</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,53</t>
+          <t>-9,85</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,16</t>
+          <t>-11,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 11,58</t>
+          <t>-2,17; 11,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 25,32</t>
+          <t>11,52; 24,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -5,39</t>
+          <t>-20,95; -4,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 7,51</t>
+          <t>-5,1; 7,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,19</t>
+          <t>6,8; 19,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,88; -3,37</t>
+          <t>-19,02; -2,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 7,29</t>
+          <t>-1,64; 7,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 20,8</t>
+          <t>11,31; 20,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,35; -7,06</t>
+          <t>-17,4; -5,28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-29,55%</t>
+          <t>-24,74%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-22,47%</t>
+          <t>-17,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-26,58%</t>
+          <t>-21,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 24,61</t>
+          <t>-4,05; 23,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,0; 53,51</t>
+          <t>20,46; 52,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,35; -11,47</t>
+          <t>-39,97; -7,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 14,37</t>
+          <t>-8,55; 14,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 36,69</t>
+          <t>11,91; 36,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -6,76</t>
+          <t>-32,61; -4,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 14,4</t>
+          <t>-2,9; 14,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,48; 40,77</t>
+          <t>20,37; 40,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -13,6</t>
+          <t>-31,73; -10,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,03</t>
+          <t>-3,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,25</t>
+          <t>-7,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,28</t>
+          <t>-5,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 4,81</t>
+          <t>-6,52; 4,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 21,63</t>
+          <t>11,78; 21,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 1,88</t>
+          <t>-10,74; 3,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 14,14</t>
+          <t>2,91; 14,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 21,7</t>
+          <t>10,71; 22,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,75; -7,83</t>
+          <t>-13,78; -1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 7,11</t>
+          <t>-0,75; 7,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 20,24</t>
+          <t>12,59; 20,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,4; -5,49</t>
+          <t>-10,38; -1,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,59%</t>
+          <t>-6,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-28,39%</t>
+          <t>-13,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-19,47%</t>
+          <t>-10,18%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 8,55</t>
+          <t>-10,49; 7,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 38,45</t>
+          <t>19,31; 38,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 2,98</t>
+          <t>-17,85; 6,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 26,05</t>
+          <t>4,83; 26,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 39,57</t>
+          <t>17,91; 41,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,37; -14,14</t>
+          <t>-23,1; -2,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 12,9</t>
+          <t>-1,23; 13,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,61; 35,97</t>
+          <t>21,05; 36,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -9,66</t>
+          <t>-17,61; -2,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-3,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,73</t>
+          <t>-0,79; 10,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,12</t>
+          <t>7,81; 18,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 1,45</t>
+          <t>-9,38; 2,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 10,84</t>
+          <t>0,39; 10,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 18,16</t>
+          <t>7,37; 17,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 0,34</t>
+          <t>-8,87; 1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,7</t>
+          <t>1,41; 9,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 16,12</t>
+          <t>9,12; 16,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; -0,74</t>
+          <t>-7,72; 0,61</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-7,34%</t>
+          <t>-4,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,51%</t>
+          <t>-6,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,9%</t>
+          <t>-5,69%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 16,96</t>
+          <t>-1,24; 18,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,41; 31,41</t>
+          <t>12,14; 32,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 2,58</t>
+          <t>-14,64; 4,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 19,15</t>
+          <t>0,95; 19,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,52; 32,51</t>
+          <t>11,95; 31,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 0,48</t>
+          <t>-13,99; 1,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 14,94</t>
+          <t>2,34; 15,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,08; 27,75</t>
+          <t>14,85; 28,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -1,27</t>
+          <t>-12,37; 1,08</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-21,6</t>
+          <t>-5,5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,69</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,48</t>
+          <t>-3,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 7,16</t>
+          <t>-4,58; 7,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 19,31</t>
+          <t>8,41; 19,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,94; -3,64</t>
+          <t>-10,5; 0,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,13; 16,5</t>
+          <t>5,08; 16,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,11; 21,22</t>
+          <t>9,79; 20,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -0,28</t>
+          <t>-7,69; 2,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,38</t>
+          <t>2,34; 10,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,73; 18,29</t>
+          <t>11,08; 19,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-33,71; -3,8</t>
+          <t>-7,91; -0,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-34,72%</t>
+          <t>-8,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-9,25%</t>
+          <t>-4,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-23,41%</t>
+          <t>-6,43%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 11,97</t>
+          <t>-6,98; 12,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 32,99</t>
+          <t>12,7; 33,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,93; -5,99</t>
+          <t>-16,34; 1,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,92; 28,38</t>
+          <t>7,92; 28,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,54; 36,28</t>
+          <t>15,15; 36,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -0,58</t>
+          <t>-11,77; 4,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 17,47</t>
+          <t>3,61; 17,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,68; 30,62</t>
+          <t>16,9; 32,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,07; -6,16</t>
+          <t>-12,44; -0,55</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,8</t>
+          <t>-3,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-2,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,65</t>
+          <t>-11,87; 2,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,09; 16,16</t>
+          <t>3,04; 15,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 3,57</t>
+          <t>-7,58; 4,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 9,35</t>
+          <t>-3,91; 9,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,72; 18,38</t>
+          <t>5,86; 18,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 2,72</t>
+          <t>-8,78; 2,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,88</t>
+          <t>-5,3; 3,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,11; 15,33</t>
+          <t>6,22; 15,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 1,69</t>
+          <t>-6,6; 1,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,92%</t>
+          <t>-2,97%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>-4,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,13%</t>
+          <t>-3,83%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 4,39</t>
+          <t>-17,56; 3,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,67; 26,95</t>
+          <t>4,58; 26,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 5,78</t>
+          <t>-11,33; 7,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 14,98</t>
+          <t>-5,45; 14,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,27; 29,91</t>
+          <t>8,43; 30,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 4,39</t>
+          <t>-12,35; 3,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 6,3</t>
+          <t>-7,94; 5,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,19; 24,56</t>
+          <t>9,26; 25,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 2,58</t>
+          <t>-9,71; 2,79</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,46</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>-3,51</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>-4,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 7,51</t>
+          <t>-8,09; 6,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 12,34</t>
+          <t>-3,53; 11,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 2,25</t>
+          <t>-12,23; 1,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 13,05</t>
+          <t>-0,75; 13,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,68; 22,4</t>
+          <t>9,66; 22,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 27,38</t>
+          <t>-9,7; 2,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 7,86</t>
+          <t>-2,66; 7,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,43</t>
+          <t>5,66; 15,56</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 18,39</t>
+          <t>-8,11; 0,37</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-8,1%</t>
+          <t>-7,87%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>-5,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>-6,54%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 11,87</t>
+          <t>-11,42; 10,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 19,57</t>
+          <t>-4,87; 18,52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 2,99</t>
+          <t>-17,07; 1,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 21,27</t>
+          <t>-1,18; 22,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,38; 36,91</t>
+          <t>14,27; 36,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 46,58</t>
+          <t>-14,18; 3,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 12,43</t>
+          <t>-3,89; 12,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8,02; 24,59</t>
+          <t>8,12; 24,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 29,38</t>
+          <t>-11,91; 0,48</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-4,99</t>
+          <t>-4,91</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 7,61</t>
+          <t>-9,78; 7,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 13,07</t>
+          <t>-2,16; 12,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 2,58</t>
+          <t>-12,78; 2,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 5,05</t>
+          <t>-9,41; 4,88</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,38; 20,75</t>
+          <t>6,86; 21,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 7,23</t>
+          <t>-5,52; 7,1</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 3,48</t>
+          <t>-7,16; 3,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,65; 15,82</t>
+          <t>5,75; 15,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 3,46</t>
+          <t>-6,17; 3,03</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-6,8%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,15%</t>
+          <t>-2,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 11,53</t>
+          <t>-12,96; 10,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 19,54</t>
+          <t>-2,75; 19,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 3,8</t>
+          <t>-16,32; 3,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 7,57</t>
+          <t>-12,52; 7,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,91; 31,62</t>
+          <t>9,12; 32,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 11,19</t>
+          <t>-7,42; 10,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 5,13</t>
+          <t>-9,85; 5,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>7,68; 23,56</t>
+          <t>7,89; 23,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 5,12</t>
+          <t>-8,37; 4,52</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-8,8</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,78</t>
+          <t>-3,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,76</t>
+          <t>-1,0; 3,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,97; 15,62</t>
+          <t>10,95; 15,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -3,79</t>
+          <t>-6,47; -1,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,76</t>
+          <t>3,27; 7,91</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,21</t>
+          <t>12,68; 17,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 4,94</t>
+          <t>-5,31; -0,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,19</t>
+          <t>1,79; 5,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>12,47; 15,73</t>
+          <t>12,37; 15,65</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -1,77</t>
+          <t>-5,18; -1,71</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-14,51%</t>
+          <t>-6,09%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-4,77%</t>
+          <t>-4,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-9,48%</t>
+          <t>-5,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,36</t>
+          <t>-1,66; 5,88</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>17,65; 26,52</t>
+          <t>17,75; 26,05</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-32,62; -6,3</t>
+          <t>-10,53; -1,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,03</t>
+          <t>5,19; 13,07</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,3; 28,95</t>
+          <t>20,29; 28,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 8,22</t>
+          <t>-8,45; -1,28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,61</t>
+          <t>2,91; 8,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>20,29; 26,39</t>
+          <t>19,85; 26,0</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -2,9</t>
+          <t>-8,4; -2,82</t>
         </is>
       </c>
     </row>
